--- a/projects/projects.xlsx
+++ b/projects/projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/lasai_barrenadataleb_kuleuven_be/Documents/Documentos e informacion/Trabajo/Webpage_quarto - AI/projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_DC12F13E0049E1E8D0E634C5AB7C1893925924AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EADC2DF-8775-4073-877E-842AF7FA2CCB}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_DC12F13E0049E1E8D0E634C5AB7C1893925924AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F9BD4F0-FCBE-4605-A6B9-4E9C7F109B2F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
   <si>
     <t>Title</t>
   </si>
@@ -224,6 +224,18 @@
   </si>
   <si>
     <t>https://fwo.be/en/results-outreach/announcement-of-results/announcement-of-results-2026/</t>
+  </si>
+  <si>
+    <t>PhD defended</t>
+  </si>
+  <si>
+    <t>KU Leuven</t>
+  </si>
+  <si>
+    <t>Thesis succesfully defended at KU Leuven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kuleuven.be/doctoraatsverdediging/fiches/3M22/3M220564.htm </t>
   </si>
 </sst>
 </file>
@@ -568,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="68.109375" bestFit="1" customWidth="1"/>
@@ -903,6 +915,29 @@
         <v>67</v>
       </c>
     </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13">
+        <v>2026</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{86CCA619-8639-4883-88CF-6F48E60B3B3E}"/>
@@ -910,8 +945,9 @@
     <hyperlink ref="I5" r:id="rId3" xr:uid="{E9EADC20-71EA-4F4F-81CC-AEE34ABDF067}"/>
     <hyperlink ref="I6" r:id="rId4" xr:uid="{2CCF4F24-A133-4C55-A6DF-62FB4A42C951}"/>
     <hyperlink ref="I7" r:id="rId5" xr:uid="{BE06E808-1A4A-4ADB-8930-08BCEA1A2561}"/>
+    <hyperlink ref="G13" r:id="rId6" xr:uid="{7B16A370-86D8-41CC-8290-FC4DAB5C4318}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId7"/>
 </worksheet>
 </file>